--- a/data/raw/Character.xlsx
+++ b/data/raw/Character.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noraammann/Documents/Cloned_GitHub/daschland-scripts/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61712A5-F088-EC48-A462-9BFDCEECA348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86049C8-A52A-0047-8AAC-C5D8B41F46D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2562,7 +2562,6 @@
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Name EN" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{87401003-6566-394F-A8FB-030450F289E5}" name="Wikidata Link" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Name DE" dataDxfId="12"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Name FR" dataDxfId="11"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name IT" dataDxfId="10"/>
@@ -2574,6 +2573,7 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Alternative Name" dataDxfId="4"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Image ID" dataDxfId="3"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Keyword" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{87401003-6566-394F-A8FB-030450F289E5}" name="Wikidata Link" dataDxfId="0"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Authorship Resource" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2763,15 +2763,16 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="5" customWidth="1"/>
-    <col min="2" max="6" width="26.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="136" style="5" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="44.6640625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="125" style="17" customWidth="1"/>
-    <col min="12" max="12" width="46.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="35.1640625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="132.33203125" style="5" customWidth="1"/>
+    <col min="2" max="5" width="26.6640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="136" style="5" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="44.6640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="125" style="17" customWidth="1"/>
+    <col min="11" max="11" width="46.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35.1640625" style="5" customWidth="1"/>
+    <col min="13" max="13" width="132.33203125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="26.6640625" style="5" customWidth="1"/>
     <col min="15" max="15" width="56.6640625" style="5" customWidth="1"/>
     <col min="16" max="16" width="8" style="1" customWidth="1"/>
     <col min="17" max="17" width="12.6640625" style="1" customWidth="1"/>
@@ -2786,40 +2787,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>13</v>
@@ -2833,7 +2834,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>15</v>
@@ -2842,29 +2843,29 @@
         <v>15</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>19</v>
-      </c>
       <c r="L2" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="5" t="s">
         <v>21</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>574</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>22</v>
@@ -2878,40 +2879,40 @@
         <v>24</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>545</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>22</v>
@@ -2925,38 +2926,38 @@
         <v>36</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>552</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>22</v>
@@ -2970,40 +2971,40 @@
         <v>47</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>556</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>22</v>
@@ -3017,40 +3018,40 @@
         <v>58</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N6" s="6" t="s">
         <v>558</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>22</v>
@@ -3064,40 +3065,40 @@
         <v>69</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="N7" s="6" t="s">
         <v>560</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>22</v>
@@ -3111,38 +3112,38 @@
         <v>80</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>559</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>22</v>
@@ -3156,38 +3157,38 @@
         <v>92</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="N9" s="6" t="s">
         <v>551</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>22</v>
@@ -3201,38 +3202,38 @@
         <v>103</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="N10" s="6" t="s">
         <v>561</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>22</v>
@@ -3246,38 +3247,38 @@
         <v>114</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="N11" s="6" t="s">
         <v>553</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>22</v>
@@ -3291,37 +3292,37 @@
         <v>124</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>566</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="O12" s="5" t="s">
         <v>22</v>
@@ -3335,7 +3336,7 @@
         <v>134</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>544</v>
+        <v>134</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>134</v>
@@ -3344,29 +3345,29 @@
         <v>134</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6" t="s">
+      <c r="G13" s="6"/>
+      <c r="H13" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="J13" s="13" t="s">
         <v>137</v>
       </c>
+      <c r="K13" s="5" t="s">
+        <v>138</v>
+      </c>
       <c r="L13" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="N13" s="5" t="s">
         <v>140</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>544</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>22</v>
@@ -3380,35 +3381,35 @@
         <v>142</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="N14" s="6" t="s">
         <v>570</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="O14" s="5" t="s">
         <v>22</v>
@@ -3422,38 +3423,38 @@
         <v>152</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="N15" s="6" t="s">
         <v>546</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>22</v>
@@ -3467,7 +3468,7 @@
         <v>163</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>547</v>
+        <v>163</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>163</v>
@@ -3476,31 +3477,31 @@
         <v>163</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="G16" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="H16" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="I16" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="J16" s="13" t="s">
         <v>166</v>
       </c>
+      <c r="K16" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="L16" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="N16" s="5" t="s">
         <v>169</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>547</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>22</v>
@@ -3514,37 +3515,37 @@
         <v>171</v>
       </c>
       <c r="C17" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="N17" s="6" t="s">
         <v>562</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="O17" s="5" t="s">
         <v>22</v>
@@ -3558,38 +3559,38 @@
         <v>181</v>
       </c>
       <c r="C18" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="G18" s="9"/>
+      <c r="H18" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="N18" s="6" t="s">
         <v>563</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H18" s="9"/>
-      <c r="I18" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="O18" s="5" t="s">
         <v>22</v>
@@ -3603,38 +3604,38 @@
         <v>192</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="G19" s="9"/>
+      <c r="H19" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="N19" s="6" t="s">
         <v>554</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="O19" s="5" t="s">
         <v>22</v>
@@ -3648,35 +3649,35 @@
         <v>203</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="G20" s="9"/>
+      <c r="H20" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="N20" s="6" t="s">
         <v>555</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="H20" s="9"/>
-      <c r="I20" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="N20" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="O20" s="5" t="s">
         <v>22</v>
@@ -3690,7 +3691,7 @@
         <v>213</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>564</v>
+        <v>213</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>213</v>
@@ -3699,25 +3700,25 @@
         <v>213</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="G21" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="I21" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="J21" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="K21" s="5" t="s">
         <v>217</v>
       </c>
+      <c r="M21" s="5" t="s">
+        <v>218</v>
+      </c>
       <c r="N21" s="5" t="s">
-        <v>218</v>
+        <v>564</v>
       </c>
       <c r="O21" s="5" t="s">
         <v>22</v>
@@ -3731,37 +3732,37 @@
         <v>220</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="N22" s="5" t="s">
         <v>550</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>229</v>
       </c>
       <c r="O22" s="5" t="s">
         <v>22</v>
@@ -3775,7 +3776,7 @@
         <v>231</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>548</v>
+        <v>231</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>231</v>
@@ -3784,28 +3785,28 @@
         <v>231</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="H23" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="K23" s="13" t="s">
+      <c r="J23" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="L23" s="5" t="s">
+      <c r="K23" s="5" t="s">
         <v>235</v>
       </c>
+      <c r="M23" s="5" t="s">
+        <v>236</v>
+      </c>
       <c r="N23" s="5" t="s">
-        <v>236</v>
+        <v>548</v>
       </c>
       <c r="O23" s="5" t="s">
         <v>22</v>
@@ -3819,37 +3820,37 @@
         <v>238</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="N24" s="5" t="s">
         <v>549</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>229</v>
       </c>
       <c r="O24" s="5" t="s">
         <v>22</v>
@@ -3863,31 +3864,31 @@
         <v>247</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="N25" s="5" t="s">
         <v>575</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>253</v>
       </c>
       <c r="O25" s="5" t="s">
         <v>22</v>
@@ -3901,7 +3902,7 @@
         <v>255</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>576</v>
+        <v>255</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>255</v>
@@ -3910,25 +3911,25 @@
         <v>255</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="G26" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="I26" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="K26" s="13" t="s">
+      <c r="J26" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="L26" s="5" t="s">
+      <c r="K26" s="5" t="s">
         <v>259</v>
       </c>
+      <c r="M26" s="5" t="s">
+        <v>253</v>
+      </c>
       <c r="N26" s="5" t="s">
-        <v>253</v>
+        <v>576</v>
       </c>
       <c r="O26" s="5" t="s">
         <v>22</v>
@@ -3942,34 +3943,34 @@
         <v>261</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="N27" s="5" t="s">
         <v>577</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="N27" s="5" t="s">
-        <v>269</v>
       </c>
       <c r="O27" s="5" t="s">
         <v>22</v>
@@ -3983,34 +3984,34 @@
         <v>271</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="N28" s="5" t="s">
         <v>557</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="N28" s="5" t="s">
-        <v>279</v>
       </c>
       <c r="O28" s="5" t="s">
         <v>22</v>
@@ -4024,35 +4025,35 @@
         <v>281</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="H29" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="N29" s="5" t="s">
         <v>578</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="H29" s="12"/>
-      <c r="I29" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="N29" s="5" t="s">
-        <v>289</v>
       </c>
       <c r="O29" s="5" t="s">
         <v>22</v>
@@ -4065,31 +4066,31 @@
       <c r="B30" s="5" t="s">
         <v>291</v>
       </c>
+      <c r="C30" s="5" t="s">
+        <v>292</v>
+      </c>
       <c r="D30" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="G30" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="H30" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="I30" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="K30" s="13" t="s">
+      <c r="J30" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="L30" s="5" t="s">
+      <c r="K30" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="N30" s="5" t="s">
+      <c r="M30" s="5" t="s">
         <v>298</v>
       </c>
       <c r="O30" s="5" t="s">
@@ -4103,34 +4104,34 @@
       <c r="B31" s="5" t="s">
         <v>300</v>
       </c>
+      <c r="C31" s="5" t="s">
+        <v>301</v>
+      </c>
       <c r="D31" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="G31" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="H31" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="I31" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="K31" s="13" t="s">
+      <c r="J31" s="13" t="s">
         <v>306</v>
       </c>
+      <c r="K31" s="5" t="s">
+        <v>307</v>
+      </c>
       <c r="L31" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="N31" s="5" t="s">
         <v>309</v>
       </c>
       <c r="O31" s="5" t="s">
@@ -4144,34 +4145,34 @@
       <c r="B32" s="5" t="s">
         <v>311</v>
       </c>
+      <c r="C32" s="5" t="s">
+        <v>312</v>
+      </c>
       <c r="D32" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="G32" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="I32" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="K32" s="13" t="s">
+      <c r="J32" s="13" t="s">
         <v>317</v>
       </c>
+      <c r="K32" s="5" t="s">
+        <v>318</v>
+      </c>
       <c r="L32" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="N32" s="5" t="s">
         <v>309</v>
       </c>
       <c r="O32" s="5" t="s">
@@ -4185,34 +4186,34 @@
       <c r="B33" s="5" t="s">
         <v>321</v>
       </c>
+      <c r="C33" s="5" t="s">
+        <v>322</v>
+      </c>
       <c r="D33" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="G33" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="H33" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="I33" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="K33" s="18" t="s">
+      <c r="J33" s="18" t="s">
         <v>327</v>
       </c>
+      <c r="K33" s="5" t="s">
+        <v>328</v>
+      </c>
       <c r="L33" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="N33" s="5" t="s">
         <v>330</v>
       </c>
       <c r="O33" s="5" t="s">
@@ -4227,34 +4228,34 @@
         <v>332</v>
       </c>
       <c r="C34" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="L34" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="N34" s="5" t="s">
         <v>579</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K34" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="M34" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="N34" s="5" t="s">
-        <v>340</v>
       </c>
       <c r="O34" s="5" t="s">
         <v>22</v>
@@ -4267,28 +4268,28 @@
       <c r="B35" s="5" t="s">
         <v>342</v>
       </c>
+      <c r="C35" s="5" t="s">
+        <v>343</v>
+      </c>
       <c r="D35" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="G35" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K35" s="13" t="s">
+      <c r="J35" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="L35" s="5" t="s">
+      <c r="K35" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="N35" s="5" t="s">
+      <c r="M35" s="5" t="s">
         <v>349</v>
       </c>
       <c r="O35" s="5" t="s">
@@ -4302,34 +4303,34 @@
       <c r="B36" s="5" t="s">
         <v>351</v>
       </c>
+      <c r="C36" s="5" t="s">
+        <v>352</v>
+      </c>
       <c r="D36" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="G36" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="I36" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="K36" s="13" t="s">
+      <c r="J36" s="13" t="s">
         <v>357</v>
       </c>
+      <c r="K36" s="5" t="s">
+        <v>358</v>
+      </c>
       <c r="L36" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="N36" s="5" t="s">
         <v>360</v>
       </c>
       <c r="O36" s="5" t="s">
@@ -4343,31 +4344,31 @@
       <c r="B37" s="5" t="s">
         <v>362</v>
       </c>
+      <c r="C37" s="5" t="s">
+        <v>363</v>
+      </c>
       <c r="D37" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="G37" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="H37" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K37" s="13" t="s">
+      <c r="J37" s="13" t="s">
         <v>367</v>
       </c>
+      <c r="K37" s="5" t="s">
+        <v>368</v>
+      </c>
       <c r="L37" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="N37" s="5" t="s">
         <v>370</v>
       </c>
       <c r="O37" s="5" t="s">
@@ -4381,31 +4382,31 @@
       <c r="B38" s="5" t="s">
         <v>372</v>
       </c>
+      <c r="C38" s="5" t="s">
+        <v>373</v>
+      </c>
       <c r="D38" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="G38" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="I38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K38" s="13" t="s">
+      <c r="J38" s="13" t="s">
         <v>377</v>
       </c>
+      <c r="K38" s="5" t="s">
+        <v>378</v>
+      </c>
       <c r="L38" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="N38" s="5" t="s">
         <v>380</v>
       </c>
       <c r="O38" s="5" t="s">
@@ -4420,34 +4421,34 @@
         <v>382</v>
       </c>
       <c r="C39" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="N39" s="5" t="s">
         <v>565</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K39" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="L39" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="N39" s="5" t="s">
-        <v>390</v>
       </c>
       <c r="O39" s="5" t="s">
         <v>22</v>
@@ -4460,31 +4461,31 @@
       <c r="B40" s="5" t="s">
         <v>392</v>
       </c>
+      <c r="C40" s="5" t="s">
+        <v>393</v>
+      </c>
       <c r="D40" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="G40" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K40" s="13" t="s">
+      <c r="J40" s="13" t="s">
         <v>397</v>
       </c>
+      <c r="K40" s="5" t="s">
+        <v>398</v>
+      </c>
       <c r="L40" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="N40" s="5" t="s">
         <v>400</v>
       </c>
       <c r="O40" s="5" t="s">
@@ -4498,31 +4499,31 @@
       <c r="B41" s="5" t="s">
         <v>402</v>
       </c>
+      <c r="C41" s="5" t="s">
+        <v>403</v>
+      </c>
       <c r="D41" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="G41" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="H41" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K41" s="13" t="s">
+      <c r="J41" s="13" t="s">
         <v>407</v>
       </c>
+      <c r="K41" s="5" t="s">
+        <v>408</v>
+      </c>
       <c r="L41" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="N41" s="5" t="s">
         <v>410</v>
       </c>
       <c r="O41" s="5" t="s">
@@ -4536,31 +4537,31 @@
       <c r="B42" s="5" t="s">
         <v>412</v>
       </c>
+      <c r="C42" s="5" t="s">
+        <v>413</v>
+      </c>
       <c r="D42" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="G42" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K42" s="13" t="s">
+      <c r="J42" s="13" t="s">
         <v>417</v>
       </c>
+      <c r="K42" s="5" t="s">
+        <v>418</v>
+      </c>
       <c r="L42" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="N42" s="5" t="s">
         <v>360</v>
       </c>
       <c r="O42" s="5" t="s">
@@ -4575,34 +4576,34 @@
         <v>421</v>
       </c>
       <c r="C43" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="N43" s="5" t="s">
         <v>569</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K43" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="N43" s="5" t="s">
-        <v>429</v>
       </c>
       <c r="O43" s="5" t="s">
         <v>22</v>
@@ -4616,34 +4617,34 @@
         <v>431</v>
       </c>
       <c r="C44" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="N44" s="5" t="s">
         <v>573</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K44" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="L44" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="M44" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="N44" s="5" t="s">
-        <v>439</v>
       </c>
       <c r="O44" s="5" t="s">
         <v>22</v>
@@ -4657,34 +4658,34 @@
         <v>441</v>
       </c>
       <c r="C45" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="N45" s="5" t="s">
         <v>571</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K45" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="L45" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="M45" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="N45" s="5" t="s">
-        <v>449</v>
       </c>
       <c r="O45" s="5" t="s">
         <v>22</v>
@@ -4698,34 +4699,34 @@
         <v>451</v>
       </c>
       <c r="C46" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="J46" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="N46" s="5" t="s">
         <v>580</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K46" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="L46" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="M46" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="N46" s="5" t="s">
-        <v>459</v>
       </c>
       <c r="O46" s="5" t="s">
         <v>22</v>
@@ -4739,34 +4740,34 @@
         <v>461</v>
       </c>
       <c r="C47" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J47" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="N47" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="K47" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="L47" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="M47" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="N47" s="5" t="s">
-        <v>459</v>
       </c>
       <c r="O47" s="5" t="s">
         <v>22</v>
@@ -4780,34 +4781,34 @@
         <v>469</v>
       </c>
       <c r="C48" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="J48" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="L48" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="N48" s="5" t="s">
         <v>568</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K48" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="L48" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="M48" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="N48" s="5" t="s">
-        <v>477</v>
       </c>
       <c r="O48" s="5" t="s">
         <v>22</v>
@@ -4820,31 +4821,31 @@
       <c r="B49" s="5" t="s">
         <v>479</v>
       </c>
+      <c r="C49" s="5" t="s">
+        <v>480</v>
+      </c>
       <c r="D49" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="G49" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="I49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="K49" s="13" t="s">
+      <c r="J49" s="13" t="s">
         <v>484</v>
       </c>
+      <c r="K49" s="5" t="s">
+        <v>485</v>
+      </c>
       <c r="L49" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="N49" s="5" t="s">
         <v>487</v>
       </c>
       <c r="O49" s="5" t="s">
@@ -4859,34 +4860,34 @@
         <v>489</v>
       </c>
       <c r="C50" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="L50" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="N50" s="5" t="s">
         <v>567</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="I50" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="K50" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="L50" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="M50" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="N50" s="5" t="s">
-        <v>497</v>
       </c>
       <c r="O50" s="5" t="s">
         <v>22</v>
@@ -4899,31 +4900,31 @@
       <c r="B51" s="5" t="s">
         <v>499</v>
       </c>
+      <c r="C51" s="5" t="s">
+        <v>500</v>
+      </c>
       <c r="D51" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="G51" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="I51" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="K51" s="13" t="s">
+      <c r="J51" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="L51" s="5" t="s">
+      <c r="K51" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="M51" s="14" t="s">
+      <c r="L51" s="14" t="s">
         <v>506</v>
       </c>
-      <c r="N51" s="5" t="s">
+      <c r="M51" s="5" t="s">
         <v>507</v>
       </c>
       <c r="O51" s="5" t="s">
@@ -4937,28 +4938,28 @@
       <c r="B52" s="5" t="s">
         <v>509</v>
       </c>
+      <c r="C52" s="5" t="s">
+        <v>81</v>
+      </c>
       <c r="D52" s="5" t="s">
-        <v>81</v>
+        <v>510</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="G52" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="H52" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="K52" s="13" t="s">
+      <c r="J52" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="L52" s="5" t="s">
+      <c r="K52" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="N52" s="5" t="s">
+      <c r="M52" s="5" t="s">
         <v>515</v>
       </c>
       <c r="O52" s="5" t="s">
@@ -4973,34 +4974,34 @@
         <v>517</v>
       </c>
       <c r="C53" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J53" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="L53" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="N53" s="5" t="s">
         <v>572</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K53" s="13" t="s">
-        <v>522</v>
-      </c>
-      <c r="L53" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="M53" s="12" t="s">
-        <v>524</v>
-      </c>
-      <c r="N53" s="5" t="s">
-        <v>525</v>
       </c>
       <c r="O53" s="5" t="s">
         <v>22</v>
@@ -5013,32 +5014,32 @@
       <c r="B54" s="5" t="s">
         <v>527</v>
       </c>
+      <c r="C54" s="5" t="s">
+        <v>528</v>
+      </c>
       <c r="D54" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="F54" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="G54" s="13" t="s">
+      <c r="F54" s="13" t="s">
         <v>530</v>
       </c>
-      <c r="H54" s="13"/>
-      <c r="I54" s="6" t="s">
+      <c r="G54" s="13"/>
+      <c r="H54" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K54" s="13" t="s">
+      <c r="J54" s="13" t="s">
         <v>531</v>
       </c>
-      <c r="L54" s="5" t="s">
+      <c r="K54" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="M54" s="14" t="s">
+      <c r="L54" s="14" t="s">
         <v>533</v>
       </c>
-      <c r="N54" s="5" t="s">
+      <c r="M54" s="5" t="s">
         <v>534</v>
       </c>
       <c r="O54" s="5" t="s">
@@ -5052,32 +5053,32 @@
       <c r="B55" s="5" t="s">
         <v>536</v>
       </c>
+      <c r="C55" s="5" t="s">
+        <v>537</v>
+      </c>
       <c r="D55" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="F55" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="G55" s="13" t="s">
+      <c r="F55" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="H55" s="13"/>
-      <c r="I55" s="5" t="s">
+      <c r="G55" s="13"/>
+      <c r="H55" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="K55" s="13" t="s">
+      <c r="J55" s="13" t="s">
         <v>541</v>
       </c>
-      <c r="L55" s="5" t="s">
+      <c r="K55" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="M55" s="14" t="s">
+      <c r="L55" s="14" t="s">
         <v>533</v>
       </c>
-      <c r="N55" s="5" t="s">
+      <c r="M55" s="5" t="s">
         <v>534</v>
       </c>
       <c r="O55" s="5" t="s">
@@ -5086,7 +5087,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H22" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="G22" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" fitToHeight="4" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
